--- a/output/pdf_financials_xlsx/NATN.xlsx
+++ b/output/pdf_financials_xlsx/NATN.xlsx
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.016983</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.019906</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.022067</v>
       </c>
     </row>
     <row r="119">
@@ -3237,7 +3237,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>-0.016983</v>
       </c>

--- a/output/pdf_financials_xlsx/NATN.xlsx
+++ b/output/pdf_financials_xlsx/NATN.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.024624</v>
       </c>
     </row>
     <row r="13">
@@ -870,10 +870,10 @@
         <v>-0.165794</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.082153</v>
+        <v>-0.086853</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.061884</v>
+        <v>-0.086508</v>
       </c>
     </row>
     <row r="28">
@@ -902,10 +902,10 @@
         <v>-0.165794</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.082153</v>
+        <v>-0.086853</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.061884</v>
+        <v>-0.086508</v>
       </c>
     </row>
     <row r="30">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
